--- a/いword.xlsx
+++ b/いword.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="376">
   <si>
     <t>気持ち</t>
   </si>
@@ -1273,6 +1273,24 @@
     <t>流水声，哗啦哗啦</t>
   </si>
   <si>
+    <t>くるくる</t>
+  </si>
+  <si>
+    <t>旋转</t>
+  </si>
+  <si>
+    <t>クルクル</t>
+  </si>
+  <si>
+    <t>方針がくるくる変わる</t>
+  </si>
+  <si>
+    <t>てんてん</t>
+  </si>
+  <si>
+    <t>转来转去</t>
+  </si>
+  <si>
     <t>にこにこ</t>
   </si>
   <si>
@@ -1282,22 +1300,13 @@
     <t>ニコニコアニメ</t>
   </si>
   <si>
-    <t>てんてん</t>
-  </si>
-  <si>
-    <t>转来转去</t>
-  </si>
-  <si>
     <t>ぐずぐず</t>
   </si>
   <si>
     <t>磨蹭的</t>
   </si>
   <si>
-    <t>愚図愚図</t>
-  </si>
-  <si>
-    <t>グズグズ</t>
+    <t>愚図愚図｜グズグズ</t>
   </si>
   <si>
     <t>ふわふわ</t>
@@ -1391,7 +1400,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="51">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1569,20 +1578,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -1738,13 +1733,6 @@
       <color rgb="FF00B0F0"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2050,19 +2038,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2071,131 +2068,122 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2229,7 +2217,6 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3565,7 +3552,7 @@
       <c r="E36" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F36" s="29" t="s">
+      <c r="F36" s="6" t="s">
         <v>283</v>
       </c>
       <c r="O36" s="1" t="s">
@@ -3582,7 +3569,7 @@
       <c r="E37" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="F37" s="29" t="s">
+      <c r="F37" s="6" t="s">
         <v>288</v>
       </c>
       <c r="O37" s="1" t="s">
@@ -3602,7 +3589,7 @@
       <c r="E38" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F38" s="29" t="s">
+      <c r="F38" s="6" t="s">
         <v>294</v>
       </c>
       <c r="O38" s="1" t="s">
@@ -3622,7 +3609,7 @@
       <c r="E39" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="F39" s="29" t="s">
+      <c r="F39" s="6" t="s">
         <v>300</v>
       </c>
     </row>
@@ -3633,7 +3620,7 @@
       <c r="E40" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="F40" s="29" t="s">
+      <c r="F40" s="6" t="s">
         <v>303</v>
       </c>
     </row>
@@ -3644,7 +3631,7 @@
       <c r="E41" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="F41" s="29" t="s">
+      <c r="F41" s="6" t="s">
         <v>306</v>
       </c>
       <c r="G41" s="6"/>
@@ -3667,11 +3654,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.8888888888889" customWidth="1"/>
     <col min="2" max="2" width="20.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="16.4444444444444" customWidth="1"/>
+    <col min="4" max="4" width="23.1111111111111" customWidth="1"/>
     <col min="7" max="7" width="18.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3777,8 +3766,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="7" ht="18" spans="1:8">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
         <v>337</v>
       </c>
       <c r="B7" t="s">
@@ -3787,24 +3776,24 @@
       <c r="C7" t="s">
         <v>339</v>
       </c>
+      <c r="D7" t="s">
+        <v>340</v>
+      </c>
       <c r="F7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B8" t="s">
-        <v>343</v>
-      </c>
-      <c r="C8" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="C8" t="s">
         <v>345</v>
       </c>
     </row>
@@ -3815,15 +3804,16 @@
       <c r="B9" t="s">
         <v>347</v>
       </c>
+      <c r="C9" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" ht="18" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B10" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="B10" t="s">
         <v>350</v>
       </c>
     </row>
@@ -3831,7 +3821,7 @@
       <c r="A11" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -3856,23 +3846,23 @@
       <c r="B13" t="s">
         <v>358</v>
       </c>
+      <c r="C13" s="1" t="s">
+        <v>359</v>
+      </c>
     </row>
     <row r="14" ht="18" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B15" t="s">
-        <v>362</v>
-      </c>
-      <c r="C15" s="1" t="s">
         <v>363</v>
       </c>
     </row>
@@ -3907,6 +3897,17 @@
       </c>
       <c r="C18" s="1" t="s">
         <v>372</v>
+      </c>
+    </row>
+    <row r="19" ht="18" spans="1:3">
+      <c r="A19" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B19" t="s">
+        <v>374</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>375</v>
       </c>
     </row>
   </sheetData>

--- a/いword.xlsx
+++ b/いword.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="378">
   <si>
     <t>気持ち</t>
   </si>
@@ -1291,6 +1291,12 @@
     <t>转来转去</t>
   </si>
   <si>
+    <t>ぐうぐう</t>
+  </si>
+  <si>
+    <t>呼噜呼噜，咕噜咕噜</t>
+  </si>
+  <si>
     <t>にこにこ</t>
   </si>
   <si>
@@ -1722,13 +1728,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="等线"/>
@@ -3654,7 +3660,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.8888888888889" customWidth="1"/>
@@ -3786,75 +3792,75 @@
         <v>342</v>
       </c>
     </row>
-    <row r="8" ht="18" spans="1:8">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
         <v>343</v>
       </c>
       <c r="B8" t="s">
         <v>344</v>
       </c>
-      <c r="C8" t="s">
-        <v>345</v>
-      </c>
     </row>
     <row r="9" ht="18" spans="1:8">
       <c r="A9" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B9" t="s">
         <v>346</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>347</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="D9" s="1"/>
     </row>
     <row r="10" ht="18" spans="1:8">
       <c r="A10" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B10" t="s">
         <v>349</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" s="1" t="s">
         <v>350</v>
       </c>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" ht="18" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>352</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:8">
       <c r="A12" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:8">
       <c r="A13" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B13" t="s">
         <v>357</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:8">
       <c r="A14" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B14" t="s">
         <v>360</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" s="1" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3873,41 +3879,49 @@
       <c r="B16" t="s">
         <v>365</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>366</v>
-      </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B17" t="s">
         <v>367</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B18" t="s">
         <v>370</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B19" t="s">
         <v>373</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C19" s="1" t="s">
+    </row>
+    <row r="20" ht="18" spans="1:3">
+      <c r="A20" s="1" t="s">
         <v>375</v>
+      </c>
+      <c r="B20" t="s">
+        <v>376</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>377</v>
       </c>
     </row>
   </sheetData>

--- a/いword.xlsx
+++ b/いword.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="381">
   <si>
     <t>気持ち</t>
   </si>
@@ -1027,10 +1027,13 @@
     <t>（厉害的、惊人的）</t>
   </si>
   <si>
-    <t>三角形</t>
-  </si>
-  <si>
-    <t>さんかくけい</t>
+    <t>煙たい</t>
+  </si>
+  <si>
+    <t>けむたい</t>
+  </si>
+  <si>
+    <t>（烟气熏人的）</t>
   </si>
   <si>
     <t>懐かしい</t>
@@ -1060,25 +1063,25 @@
     </r>
   </si>
   <si>
+    <t>三角形</t>
+  </si>
+  <si>
+    <t>さんかくけい</t>
+  </si>
+  <si>
+    <t>眠い</t>
+  </si>
+  <si>
+    <t>ねむい</t>
+  </si>
+  <si>
+    <t>（很困的）</t>
+  </si>
+  <si>
     <t>四角形</t>
   </si>
   <si>
     <t>しかくけい</t>
-  </si>
-  <si>
-    <t>眠い</t>
-  </si>
-  <si>
-    <t>ねむい</t>
-  </si>
-  <si>
-    <t>（很困的）</t>
-  </si>
-  <si>
-    <t>正方形</t>
-  </si>
-  <si>
-    <t>せいほうけい</t>
   </si>
   <si>
     <t>慌ただしい</t>
@@ -1099,19 +1102,34 @@
     </r>
   </si>
   <si>
+    <t>正方形</t>
+  </si>
+  <si>
+    <t>せいほうけい</t>
+  </si>
+  <si>
+    <t>狡い</t>
+  </si>
+  <si>
+    <t>ずるい</t>
+  </si>
+  <si>
+    <t>（狡猾的）</t>
+  </si>
+  <si>
     <t>長方形</t>
   </si>
   <si>
     <t>ちょうほうけい</t>
   </si>
   <si>
-    <t>狡い</t>
-  </si>
-  <si>
-    <t>ずるい</t>
-  </si>
-  <si>
-    <t>（狡猾的）</t>
+    <t>貧しい</t>
+  </si>
+  <si>
+    <t>まずしい</t>
+  </si>
+  <si>
+    <t>（贫穷的）</t>
   </si>
   <si>
     <t>円形</t>
@@ -1120,13 +1138,13 @@
     <t>えんけい</t>
   </si>
   <si>
-    <t>貧しい</t>
-  </si>
-  <si>
-    <t>まずしい</t>
-  </si>
-  <si>
-    <t>（贫穷的）</t>
+    <t>かっこ悪い</t>
+  </si>
+  <si>
+    <t>かっこわるい</t>
+  </si>
+  <si>
+    <t>（难看的）</t>
   </si>
   <si>
     <t>役に立つ</t>
@@ -1138,13 +1156,13 @@
     <t>役に立つもの</t>
   </si>
   <si>
-    <t>かっこ悪い</t>
-  </si>
-  <si>
-    <t>かっこわるい</t>
-  </si>
-  <si>
-    <t>（难看的）</t>
+    <t>申し訳ない</t>
+  </si>
+  <si>
+    <t>もうしわけない</t>
+  </si>
+  <si>
+    <t>（非常抱歉的）</t>
   </si>
   <si>
     <t>役に立たない</t>
@@ -1154,15 +1172,6 @@
   </si>
   <si>
     <t>役に立たないもの</t>
-  </si>
-  <si>
-    <t>申し訳ない</t>
-  </si>
-  <si>
-    <t>もうしわけない</t>
-  </si>
-  <si>
-    <t>（非常抱歉的）</t>
   </si>
   <si>
     <t>賢い</t>
@@ -3493,98 +3502,98 @@
       <c r="F32" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="O32" s="1" t="s">
+      <c r="O32" t="s">
         <v>264</v>
       </c>
-      <c r="P32" s="1" t="s">
+      <c r="P32" t="s">
         <v>265</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="33" ht="18" spans="4:17">
       <c r="D33" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" ht="18" spans="4:17">
       <c r="D34" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>273</v>
-      </c>
-      <c r="O34" t="s">
         <v>274</v>
       </c>
+      <c r="O34" s="1" t="s">
+        <v>275</v>
+      </c>
       <c r="P34" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35" ht="18" spans="4:17">
       <c r="D35" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="O35" s="1" t="s">
         <v>279</v>
       </c>
+      <c r="O35" t="s">
+        <v>280</v>
+      </c>
       <c r="P35" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="36" ht="18" spans="4:17">
       <c r="D36" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37" ht="18" spans="4:17">
       <c r="D37" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q37" s="1" t="s">
         <v>291</v>
       </c>
     </row>
@@ -3618,27 +3627,36 @@
       <c r="F39" s="6" t="s">
         <v>300</v>
       </c>
+      <c r="O39" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="40" ht="18" spans="4:17">
       <c r="D40" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" ht="18" spans="4:17">
       <c r="D41" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G41" s="6"/>
     </row>
@@ -3672,256 +3690,256 @@
   <sheetData>
     <row r="1" ht="18" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G4" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H4" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G5" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B6" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G6" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B7" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C7" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D7" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F7" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G7" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B8" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B9" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C9" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B10" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D10" s="1"/>
     </row>
     <row r="11" ht="18" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B13" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B14" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B15" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B16" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B18" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B19" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B20" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/いword.xlsx
+++ b/いword.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="389">
   <si>
     <t>気持ち</t>
   </si>
@@ -1192,6 +1192,15 @@
     <t>（强壮的，坚强的）</t>
   </si>
   <si>
+    <t>見っともない</t>
+  </si>
+  <si>
+    <t>みっともない</t>
+  </si>
+  <si>
+    <t>（不像样的，不体面的）</t>
+  </si>
+  <si>
     <t>わちゃわちゃ</t>
   </si>
   <si>
@@ -1403,6 +1412,21 @@
   </si>
   <si>
     <t>バラバラ</t>
+  </si>
+  <si>
+    <t>めちゃめちゃ</t>
+  </si>
+  <si>
+    <t>一塌糊涂</t>
+  </si>
+  <si>
+    <t>そわそわ</t>
+  </si>
+  <si>
+    <t>坐立难安地，慌张地</t>
+  </si>
+  <si>
+    <t>ソワソワ</t>
   </si>
 </sst>
 </file>
@@ -1737,13 +1761,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="等线"/>
@@ -3660,6 +3684,17 @@
       </c>
       <c r="G41" s="6"/>
     </row>
+    <row r="42" spans="4:17">
+      <c r="D42" t="s">
+        <v>310</v>
+      </c>
+      <c r="E42" t="s">
+        <v>311</v>
+      </c>
+      <c r="F42" t="s">
+        <v>312</v>
+      </c>
+    </row>
     <row r="46" spans="4:17">
       <c r="G46" s="6"/>
     </row>
@@ -3678,7 +3713,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.8888888888889" customWidth="1"/>
@@ -3690,256 +3725,275 @@
   <sheetData>
     <row r="1" ht="18" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B4" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="H4" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B6" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G6" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B7" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C7" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D7" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F7" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G7" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B8" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B9" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C9" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B10" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D10" s="1"/>
     </row>
     <row r="11" ht="18" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B11" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B13" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B14" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B15" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B16" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B17" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B18" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B19" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B20" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>384</v>
+      </c>
+      <c r="B21" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>386</v>
+      </c>
+      <c r="B22" t="s">
+        <v>387</v>
+      </c>
+      <c r="C22" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/いword.xlsx
+++ b/いword.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="392">
   <si>
     <t>気持ち</t>
   </si>
@@ -469,6 +469,15 @@
     <t>いたい</t>
   </si>
   <si>
+    <t>若々しい</t>
+  </si>
+  <si>
+    <t>わかわかしい</t>
+  </si>
+  <si>
+    <t>（朝气蓬勃的，年轻的）</t>
+  </si>
+  <si>
     <t>太い</t>
   </si>
   <si>
@@ -500,6 +509,12 @@
   </si>
   <si>
     <t>（痛苦的，辛苦的）</t>
+  </si>
+  <si>
+    <t>若い</t>
+  </si>
+  <si>
+    <t>わかい</t>
   </si>
   <si>
     <t>粗い</t>
@@ -917,12 +932,6 @@
     <t>（厉害的）</t>
   </si>
   <si>
-    <t>若い</t>
-  </si>
-  <si>
-    <t>わかい</t>
-  </si>
-  <si>
     <t>（年轻的）</t>
   </si>
   <si>
@@ -1761,13 +1770,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="等线"/>
@@ -3014,321 +3023,335 @@
         <v>124</v>
       </c>
       <c r="F10" s="6"/>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H10" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" t="s">
+        <v>127</v>
+      </c>
       <c r="O10" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q10" s="6"/>
       <c r="R10" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:23">
       <c r="A11" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
+      </c>
+      <c r="G11" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" t="s">
+        <v>140</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="V11" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="W11" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:23">
       <c r="A12" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G12" s="6"/>
       <c r="O12" s="24" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:23">
       <c r="A13" s="25" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G13" s="6"/>
       <c r="O13" s="5" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="Q13" s="6"/>
       <c r="U13" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="V13" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:23">
       <c r="A14" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="K14" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="P14" s="4" t="s">
         <v>45</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="U14" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:23">
       <c r="A15" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C15" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="Q15" s="6"/>
       <c r="U15" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:23">
       <c r="A16" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G16" s="1"/>
       <c r="O16" s="4" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:17">
       <c r="A17" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="Q17" s="6"/>
     </row>
     <row r="18" ht="18" spans="1:17">
       <c r="A18" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F18" t="s">
+        <v>207</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="P18" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="F18" t="s">
-        <v>202</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>196</v>
       </c>
       <c r="Q18" s="6"/>
     </row>
     <row r="19" ht="18" spans="1:17">
       <c r="D19" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F19" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G19" s="6"/>
       <c r="O19" s="4" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="Q19" s="6"/>
     </row>
     <row r="20" ht="18" spans="1:17">
       <c r="D20" s="4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="P20" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:17">
       <c r="D21" s="4" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="O21" s="4" t="s">
         <v>95</v>
@@ -3337,362 +3360,362 @@
         <v>96</v>
       </c>
       <c r="Q21" s="26" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:17">
       <c r="D22" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G22" s="6"/>
       <c r="O22" s="4" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="Q22" s="6"/>
     </row>
     <row r="23" ht="18" spans="1:17">
       <c r="D23" s="4" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="G23" s="28"/>
       <c r="O23" s="4" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Q23" s="6"/>
     </row>
     <row r="24" ht="18" spans="1:17">
       <c r="D24" s="4" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G24" s="27"/>
       <c r="O24" s="4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:17">
       <c r="D25" s="4" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:17">
       <c r="D26" s="4" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:17">
       <c r="D27" s="4" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="G27" s="1"/>
       <c r="O27" s="4" t="s">
-        <v>242</v>
+        <v>139</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:17">
       <c r="D28" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:17">
       <c r="D29" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F29" s="6"/>
       <c r="O29" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q29" s="1"/>
     </row>
     <row r="30" ht="18" spans="1:17">
       <c r="D30" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G30" s="27"/>
       <c r="O30" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:17">
       <c r="D31" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:17">
       <c r="D32" s="4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="O32" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="P32" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q32" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33" ht="18" spans="4:17">
       <c r="D33" s="4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" ht="18" spans="4:17">
       <c r="D34" s="4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" ht="18" spans="4:17">
       <c r="D35" s="4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O35" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36" ht="18" spans="4:17">
       <c r="D36" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" ht="18" spans="4:17">
       <c r="D37" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" ht="18" spans="4:17">
       <c r="D38" s="4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" ht="18" spans="4:17">
       <c r="D39" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" ht="18" spans="4:17">
       <c r="D40" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" ht="18" spans="4:17">
       <c r="D41" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G41" s="6"/>
     </row>
     <row r="42" spans="4:17">
       <c r="D42" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E42" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F42" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" spans="4:17">
@@ -3725,275 +3748,275 @@
   <sheetData>
     <row r="1" ht="18" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B4" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H4" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B5" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B6" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G6" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B7" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C7" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D7" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F7" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G7" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B9" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C9" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B10" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D10" s="1"/>
     </row>
     <row r="11" ht="18" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B11" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B13" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B14" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B15" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B16" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B18" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B19" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B21" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B22" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C22" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
